--- a/testcase_new/耗时用例记录表.xlsx
+++ b/testcase_new/耗时用例记录表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>用例路径</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -27,6 +27,18 @@
   </si>
   <si>
     <t>原因</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trunk\testcase_new\s3\java\src\test\java\com\sequoias3\object\serial\CreateObject16516.java</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5分钟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s3上传对象内容较大（2G）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -96,6 +108,74 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -107,7 +187,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="C7EDCC"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -407,10 +487,16 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
+    <row r="2" spans="1:9" ht="54">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
